--- a/artfynd/Kölavallhöjden artfynd.xlsx
+++ b/artfynd/Kölavallhöjden artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97023311</v>
+        <v>97023320</v>
       </c>
       <c r="B9" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492188</v>
+        <v>492176</v>
       </c>
       <c r="R9" t="n">
-        <v>6935756</v>
+        <v>6936105</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,15 +1550,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>gammal grannaturskog, luckig och hänglavsrik, i östsluttning</t>
+          <t>riktigt gammal grannaturskog, luckig och hänglavsrik</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>3 substratenheter # granlågor, förrötade</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1580,32 +1580,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97023317</v>
+        <v>97023311</v>
       </c>
       <c r="B10" t="n">
-        <v>5199</v>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491980</v>
+        <v>492188</v>
       </c>
       <c r="R10" t="n">
-        <v>6935834</v>
+        <v>6935756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,15 +1664,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>130-årig grannaturskog med inslag av gammal gran, luckig och hänglavsrik</t>
+          <t>gammal grannaturskog, luckig och hänglavsrik, i östsluttning</t>
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # typiska spår i senvuxen och död gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1694,32 +1694,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97023333</v>
+        <v>97023317</v>
       </c>
       <c r="B11" t="n">
-        <v>80298</v>
+        <v>5199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>388</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492179</v>
+        <v>491980</v>
       </c>
       <c r="R11" t="n">
-        <v>6936323</v>
+        <v>6935834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,15 +1778,15 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>asprik luckig blandnaturskog</t>
+          <t>130-årig grannaturskog med inslag av gammal gran, luckig och hänglavsrik</t>
         </is>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>4 substratenheter # äldre aspar</t>
+          <t>1 substratenheter # typiska spår i senvuxen och död gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97023320</v>
+        <v>97023333</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>80298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492176</v>
+        <v>492179</v>
       </c>
       <c r="R12" t="n">
-        <v>6936105</v>
+        <v>6936323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,15 +1892,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>riktigt gammal grannaturskog, luckig och hänglavsrik</t>
+          <t>asprik luckig blandnaturskog</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>3 substratenheter # granlågor, förrötade</t>
+          <t>4 substratenheter # äldre aspar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97023337</v>
+        <v>97023328</v>
       </c>
       <c r="B13" t="n">
-        <v>91909</v>
+        <v>89292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
         <v>492109</v>
       </c>
       <c r="R13" t="n">
-        <v>6936363</v>
+        <v>6936540</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,15 +2006,15 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>olikåldrig, något luckig grannaturskog</t>
+          <t>120-årig grannaturskog i svacka</t>
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>2 substratenheter # förrötade grova granlågor</t>
+          <t>1 substratenheter # förrötad granlåga av toppbruten gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2036,32 +2036,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97023341</v>
+        <v>97023327</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492160</v>
+        <v>492129</v>
       </c>
       <c r="R14" t="n">
-        <v>6936294</v>
+        <v>6936680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>asprik luckig grannaturskog</t>
+          <t>130-årig grannaturskog med mycket död ved i bäckmiljö</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre asp</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2150,32 +2150,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97023336</v>
+        <v>97023322</v>
       </c>
       <c r="B15" t="n">
-        <v>80432</v>
+        <v>92509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492142</v>
+        <v>491970</v>
       </c>
       <c r="R15" t="n">
-        <v>6936348</v>
+        <v>6936448</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,15 +2234,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>olikåldrig, något luckig grannaturskog, i halvljust läge</t>
+          <t>130-årig grannaturskog med lövinslag i östsluttning</t>
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>2 substratenheter # gammal flerstammig sälg med stor sockel och grangrenar där under</t>
+          <t>1 substratenheter # gammal sälg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97023340</v>
+        <v>97023325</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492089</v>
+        <v>492139</v>
       </c>
       <c r="R16" t="n">
-        <v>6936231</v>
+        <v>6936720</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,15 +2348,15 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>olikåldrig och tätare grannaturskog med lövinslag i fuktsvacka</t>
+          <t>130-årig grannaturskog med mycket död ved i bäckmiljö</t>
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>7 substratenheter # gamla sälgar, delvis flerstammiga</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97023342</v>
+        <v>97023337</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492168</v>
+        <v>492109</v>
       </c>
       <c r="R17" t="n">
-        <v>6936250</v>
+        <v>6936363</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,12 +2462,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>asprik luckig grannaturskog</t>
-        </is>
+          <t>olikåldrig, något luckig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>äldre aspar</t>
+          <t>2 substratenheter # förrötade grova granlågor</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2489,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97023335</v>
+        <v>97023341</v>
       </c>
       <c r="B18" t="n">
-        <v>80461</v>
+        <v>91920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,21 +2503,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2524,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492142</v>
+        <v>492160</v>
       </c>
       <c r="R18" t="n">
-        <v>6936348</v>
+        <v>6936294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2576,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>olikåldrig, något luckig grannaturskog, i halvljust läge</t>
+          <t>asprik luckig grannaturskog</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2581,7 +2584,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal flerstammig sälg med stor sockel</t>
+          <t>1 substratenheter # äldre asp</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2603,32 +2606,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97023334</v>
+        <v>97023332</v>
       </c>
       <c r="B19" t="n">
-        <v>80467</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2638,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492142</v>
+        <v>492200</v>
       </c>
       <c r="R19" t="n">
-        <v>6936348</v>
+        <v>6936447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,15 +2690,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>olikåldrig, något luckig grannaturskog, i halvljust läge</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
+          <t>mycket gammal hänglavsrik grannaturskog på frisk rismark</t>
+        </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal flerstammig sälg med stor sockel</t>
+          <t>riktigt gamla granar</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97023338</v>
+        <v>97023323</v>
       </c>
       <c r="B20" t="n">
-        <v>5199</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492103</v>
+        <v>491981</v>
       </c>
       <c r="R20" t="n">
-        <v>6936340</v>
+        <v>6936657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,12 +2801,15 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>olikåldrig, något luckig grannaturskog</t>
-        </is>
+          <t>130-årig grannaturskog med lövinslag i östsluttning</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>10</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>typiska spår i förrötad granlåga efter senvuxen gammal gran</t>
+          <t>10 substratenheter # gamla sälgar spridda</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2828,32 +2831,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97023343</v>
+        <v>97023331</v>
       </c>
       <c r="B21" t="n">
-        <v>80392</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,10 +2866,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492168</v>
+        <v>492170</v>
       </c>
       <c r="R21" t="n">
-        <v>6936250</v>
+        <v>6936506</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,12 +2915,15 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>asprik luckig grannaturskog</t>
-        </is>
+          <t>asprik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>3</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>äldre aspar</t>
+          <t>3 substratenheter # äldre aspar</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2939,10 +2945,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97023328</v>
+        <v>97023336</v>
       </c>
       <c r="B22" t="n">
-        <v>89292</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2974,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492109</v>
+        <v>492142</v>
       </c>
       <c r="R22" t="n">
-        <v>6936540</v>
+        <v>6936348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3023,15 +3029,15 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>120-årig grannaturskog i svacka</t>
+          <t>olikåldrig, något luckig grannaturskog, i halvljust läge</t>
         </is>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av toppbruten gran</t>
+          <t>2 substratenheter # gammal flerstammig sälg med stor sockel och grangrenar där under</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3053,10 +3059,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97023327</v>
+        <v>97023340</v>
       </c>
       <c r="B23" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,21 +3070,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3094,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492129</v>
+        <v>492089</v>
       </c>
       <c r="R23" t="n">
-        <v>6936680</v>
+        <v>6936231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3137,15 +3143,15 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>130-årig grannaturskog med mycket död ved i bäckmiljö</t>
+          <t>olikåldrig och tätare grannaturskog med lövinslag i fuktsvacka</t>
         </is>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga</t>
+          <t>7 substratenheter # gamla sälgar, delvis flerstammiga</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3167,32 +3173,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97023322</v>
+        <v>97023342</v>
       </c>
       <c r="B24" t="n">
-        <v>92509</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3202,10 +3208,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491970</v>
+        <v>492168</v>
       </c>
       <c r="R24" t="n">
-        <v>6936448</v>
+        <v>6936250</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,15 +3257,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>130-årig grannaturskog med lövinslag i östsluttning</t>
-        </is>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
+          <t>asprik luckig grannaturskog</t>
+        </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg</t>
+          <t>äldre aspar</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3281,32 +3284,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97023325</v>
+        <v>97023335</v>
       </c>
       <c r="B25" t="n">
-        <v>91909</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,10 +3319,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492139</v>
+        <v>492142</v>
       </c>
       <c r="R25" t="n">
-        <v>6936720</v>
+        <v>6936348</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,7 +3368,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>130-årig grannaturskog med mycket död ved i bäckmiljö</t>
+          <t>olikåldrig, något luckig grannaturskog, i halvljust läge</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3373,7 +3376,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga</t>
+          <t>1 substratenheter # gammal flerstammig sälg med stor sockel</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3395,32 +3398,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97023332</v>
+        <v>97023330</v>
       </c>
       <c r="B26" t="n">
-        <v>83307</v>
+        <v>80467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3430,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492200</v>
+        <v>492170</v>
       </c>
       <c r="R26" t="n">
-        <v>6936447</v>
+        <v>6936506</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3479,12 +3482,15 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>mycket gammal hänglavsrik grannaturskog på frisk rismark</t>
-        </is>
+          <t>asprik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>3</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>riktigt gamla granar</t>
+          <t>3 substratenheter # äldre aspar</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3506,32 +3512,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97023323</v>
+        <v>97023334</v>
       </c>
       <c r="B27" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3541,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491981</v>
+        <v>492142</v>
       </c>
       <c r="R27" t="n">
-        <v>6936657</v>
+        <v>6936348</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,15 +3596,15 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>130-årig grannaturskog med lövinslag i östsluttning</t>
+          <t>olikåldrig, något luckig grannaturskog, i halvljust läge</t>
         </is>
       </c>
       <c r="AN27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>10 substratenheter # gamla sälgar spridda</t>
+          <t>1 substratenheter # gammal flerstammig sälg med stor sockel</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3620,32 +3626,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97023331</v>
+        <v>97023338</v>
       </c>
       <c r="B28" t="n">
-        <v>80432</v>
+        <v>5199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3655,10 +3661,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492170</v>
+        <v>492103</v>
       </c>
       <c r="R28" t="n">
-        <v>6936506</v>
+        <v>6936340</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,15 +3710,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>asprik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AN28" t="n">
-        <v>3</v>
+          <t>olikåldrig, något luckig grannaturskog</t>
+        </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>3 substratenheter # äldre aspar</t>
+          <t>typiska spår i förrötad granlåga efter senvuxen gammal gran</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3734,32 +3737,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97023330</v>
+        <v>97023326</v>
       </c>
       <c r="B29" t="n">
-        <v>80467</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3769,10 +3772,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492170</v>
+        <v>492066</v>
       </c>
       <c r="R29" t="n">
-        <v>6936506</v>
+        <v>6936699</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,15 +3821,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>asprik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AN29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>3 substratenheter # äldre aspar</t>
+          <t>130-årig grannaturskog med lövinslag i blockig östsluttning</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3848,32 +3843,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97023326</v>
+        <v>97023343</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>80392</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3883,10 +3878,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492066</v>
+        <v>492168</v>
       </c>
       <c r="R30" t="n">
-        <v>6936699</v>
+        <v>6936250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3927,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>130-årig grannaturskog med lövinslag i blockig östsluttning</t>
+          <t>asprik luckig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>äldre aspar</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
